--- a/budget/baerheim/baerheim-golfklubb-budget.xlsx
+++ b/budget/baerheim/baerheim-golfklubb-budget.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,14 +17,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sponsorship'!$A$1:$F$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Scenarios'!$A$1:$F$10</definedName>
   </definedNames>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0 &quot;NOK&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0\ &quot;NOK&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -36,20 +35,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="FF666666"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
@@ -61,22 +71,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017324D"/>
+        <fgColor rgb="FF17324D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,22 +99,20 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color rgb="00B7B7B7"/>
+        <color rgb="FFB7B7B7"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -123,22 +131,36 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F4CCCC"/>
+          <fgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E2F0D9"/>
+          <fgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -505,341 +527,341 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" style="16" min="1" max="1"/>
+    <col width="20" customWidth="1" style="16" min="2" max="2"/>
+    <col width="58" customWidth="1" style="16" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Event Budget Inputs</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="16">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Edit yellow cells. Blue and green cells contain formulas or calculated outputs.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="16">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Event name</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Hjemmebane 2027</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Name used in the workbook</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Bærheim Golfpark / Sandnes Golfklubb</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Course or venue</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Total players</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Maximum planned field</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Company share</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Share of places included in company packages</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Company players</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <f>ROUND(B7*B8,0)</f>
         <v/>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Paying students</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <f>B7-B9</f>
         <v/>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Contingency rate</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Applied to cash expenses</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Target cash sponsorship</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Do not include in-kind prizes</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Provisional student fee</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="6" t="n">
         <v>800</v>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Public registration price</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="16" ht="16" customHeight="1" s="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Budget result</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Expense subtotal</t>
         </is>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="7">
         <f>Costs!E19</f>
         <v/>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Before contingency</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="7">
         <f>Costs!E20</f>
         <v/>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Reserve for uncertainty</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Working total</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="7">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Total cash requirement</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Package revenue</t>
         </is>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="7">
         <f>Sponsorship!F10</f>
         <v/>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Revenue from package allocation</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Company places allocated</t>
         </is>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="8">
         <f>Sponsorship!E10</f>
         <v/>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Must not exceed company-player capacity</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Funding after package revenue</t>
         </is>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="7">
         <f>B19-B20</f>
         <v/>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Amount remaining for student fees or other income</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Break-even student fee</t>
         </is>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="7">
         <f>IF(B10=0,0,MAX(0,B22/B10))</f>
         <v/>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Required fee using package revenue</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Projected student revenue</t>
         </is>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="7">
         <f>B10*B13</f>
         <v/>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>At full attendance</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Projected result</t>
         </is>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="7">
         <f>B20+B24-B19</f>
         <v/>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Positive is surplus; negative is funding gap</t>
         </is>
@@ -860,7 +882,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -871,475 +893,475 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" style="16" min="1" max="1"/>
+    <col width="38" customWidth="1" style="16" min="2" max="2"/>
+    <col width="12" customWidth="1" style="16" min="3" max="3"/>
+    <col width="17" customWidth="1" style="16" min="4" max="4"/>
+    <col width="19" customWidth="1" style="16" min="5" max="5"/>
+    <col width="52" customWidth="1" style="16" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Event Costs</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="16">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Enter quantities and unit costs. Use zero for sponsor-supplied items with no event cash expense.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="16">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Cost item</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Unit cost</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Status / notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Fixed venue charge</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>No separate venue charge quoted; minimum spend must be confirmed</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Golf</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Green fees</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="D6" s="8" t="n">
+      <c r="D6" s="6" t="n">
         <v>800</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Quoted per player; includes tournament setup and shotgun start</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Dinner/food</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="6" t="n">
         <v>750</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>NOK 600 plus assumed 25% VAT; minimum 40 guests</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>On-course refreshments</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="6" t="n">
         <v>137.5</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Baguette, chocolate and soft drink at NOK 110 plus assumed 25% VAT</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Evening</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Dinner/afterparty room and AV</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Function room and projector appear available; confirm minimum spend</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Prizes</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Competition and main prizes</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Non-cash items supplied by sponsors</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Signs, badges, scorecards and stands</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Reduced allowance; course equipment and outdoor furniture are available</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Photographer/content</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="6" t="n">
         <v>8000</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="9">
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Optional planning allowance</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Insurance, first aid and permits</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D13" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="9">
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Confirm organizer and venue coverage</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Website, payment and administration</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="D14" s="6" t="n">
         <v>5000</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="9">
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Excludes development labor</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Operations</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Event staff/volunteer expenses</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="D15" s="6" t="n">
         <v>4000</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="9">
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Reduced allowance because venue assists with tournament administration</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Local transport and miscellaneous</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="8" t="n">
+      <c r="D16" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Planning allowance</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Golf</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Range balls</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="9">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Optional 30-ball warm-up allocation per player</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Food</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Dinner soft drinks and coffee</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="9">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Allowance for required venue-purchased soft drinks and coffee at dinner</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="19" ht="16" customHeight="1" s="16">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="12" t="inlineStr"/>
-      <c r="E19" s="12">
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10">
         <f>SUM(E5:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
+      <c r="F19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="15">
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="13">
         <f>E19*Inputs!B11</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>Working total</t>
         </is>
       </c>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="15">
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13">
         <f>E19+E20</f>
         <v/>
       </c>
@@ -1351,7 +1373,7 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1362,196 +1384,195 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" style="16" min="1" max="1"/>
+    <col width="18" customWidth="1" style="16" min="2" max="2"/>
+    <col width="19" customWidth="1" style="16" min="3" max="3"/>
+    <col width="17" customWidth="1" style="16" min="4" max="4"/>
+    <col width="20" customWidth="1" style="16" min="5" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Sponsorship Packages</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="16">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Package places are included benefits, not free event capacity. In-kind prizes are excluded from cash revenue.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="16">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Players included</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Packages sold</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Places allocated</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Cash revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Title Partner</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Main Partner</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="9">
+        <f>B5*D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Company Partner</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>30000</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>B6*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Supporting Partner</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <f>C5*D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>B5*D5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Company Partner</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>B6*D6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Supporting Partner</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>7500</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <f>B7*D7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Additional Package</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>B8*D8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Additional Package</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="5">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <f>B9*D9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16">
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="13">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
@@ -1584,7 +1605,7 @@
           <t>Direct event cost per player</t>
         </is>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <f>SUMIF(Costs!B5:B18,"Green fees",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Dinner/food",Costs!D5:D18)+SUMIF(Costs!B5:B18,"On-course refreshments",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Range balls",Costs!D5:D18)+SUMIF(Costs!B5:B18,"Dinner soft drinks and coffee",Costs!D5:D18)</f>
         <v/>
       </c>
@@ -1601,7 +1622,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1612,193 +1633,193 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" style="16" min="1" max="1"/>
+    <col width="20" customWidth="1" style="16" min="2" max="2"/>
+    <col width="22" customWidth="1" style="16" min="3" max="3"/>
+    <col width="18" customWidth="1" style="16" min="4" max="4"/>
+    <col width="28" customWidth="1" style="16" min="5" max="5"/>
+    <col width="35" customWidth="1" style="16" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1" s="16">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Student Fee Scenarios</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="16">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Change sponsorship values in column A to compare the required fee for paying students.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="16">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Cash sponsorship</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Working total</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Remaining funding</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>Paying students</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Break-even fee per student</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <f>MAX(0,B5-A5)</f>
         <v/>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <f>IF(D5=0,0,C5/D5)</f>
         <v/>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="6" t="n">
         <v>50000</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <f>MAX(0,B6-A6)</f>
         <v/>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <f>IF(D6=0,0,C6/D6)</f>
         <v/>
       </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="6" t="n">
         <v>75000</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="9">
         <f>MAX(0,B7-A7)</f>
         <v/>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <f>IF(D7=0,0,C7/D7)</f>
         <v/>
       </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>MAX(0,B8-A8)</f>
         <v/>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="9">
         <f>IF(D8=0,0,C8/D8)</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="6" t="n">
         <v>125000</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="9">
         <f>MAX(0,B9-A9)</f>
         <v/>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="9">
         <f>IF(D9=0,0,C9/D9)</f>
         <v/>
       </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="B10" s="11">
+      <c r="A10" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="B10" s="9">
         <f>Costs!E21</f>
         <v/>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="9">
         <f>MAX(0,B10-A10)</f>
         <v/>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="2">
         <f>Inputs!B10</f>
         <v/>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="9">
         <f>IF(D10=0,0,C10/D10)</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F10"/>
@@ -1807,6 +1828,6 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" fitToHeight="0"/>
 </worksheet>
 </file>